--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N51_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,23 +480,55 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>3.012103900303292</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.194707584161265</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3861872949219476</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7191401445019004</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W0035F0002T0006Z000C1N51.png</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
         <v>2.239729310459397</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>1.756427295157464</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3861872949219476</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7191401445019004</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.012103900303292</v>
+        <v>0.489466883799285</v>
       </c>
       <c r="D2" t="n">
-        <v>3.194707584161265</v>
+        <v>0.5191399824262056</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3861872949219476</v>
+        <v>0.06275543542481649</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7191401445019004</v>
+        <v>0.1168602734815588</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.239729310459397</v>
+        <v>0.363956012949652</v>
       </c>
       <c r="D3" t="n">
-        <v>1.756427295157464</v>
+        <v>0.285419435463088</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3861872949219476</v>
+        <v>0.06275543542481649</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7191401445019004</v>
+        <v>0.1168602734815588</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
